--- a/Proyecto/TRIMESTRE 1/04) REQUERIMIENTOS/EDITABLES/Hu .xlsx
+++ b/Proyecto/TRIMESTRE 1/04) REQUERIMIENTOS/EDITABLES/Hu .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arcangeles\Desktop\repo\Pteamgtecno\ProyectoT1\PROYECTO\04) REQUERIMIENTOS\EDITABLES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arcangeles\Desktop\new\Pteamgtecno\Proyecto\TRIMESTRE 1\04) REQUERIMIENTOS\EDITABLES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBACEDFB-3083-4673-AC96-8AB1C7D212DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E30C070-82B4-47A4-95E8-6B52CF1E8783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="2160" windowWidth="8655" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="990" yWindow="-120" windowWidth="27930" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Historia de Usuario" sheetId="3" r:id="rId1"/>
@@ -25,229 +25,166 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>Perfil</t>
-  </si>
-  <si>
-    <t># Requerimiento</t>
-  </si>
-  <si>
     <t>Necesidad</t>
   </si>
   <si>
-    <t>Propósito</t>
-  </si>
-  <si>
     <t>HU_001</t>
   </si>
   <si>
-    <t>RE_001 al RE_003</t>
-  </si>
-  <si>
     <t>Dueño</t>
   </si>
   <si>
-    <t xml:space="preserve">Poder gestionar la creacion edicion y eliminacion de usuarios </t>
-  </si>
-  <si>
-    <t>Tener un control de Empleados y clientes en su empresa</t>
-  </si>
-  <si>
     <t>HU_002</t>
   </si>
   <si>
-    <t>RE_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayudar a la secretaria a poder programar los horarios y espacio de las clases mas facilmente </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disminuir tiempo en la creacion de las clases para la programacion de las mismas </t>
-  </si>
-  <si>
     <t>HU_003</t>
   </si>
   <si>
-    <t>RE_005, RE_006</t>
-  </si>
-  <si>
-    <t>Poder hacer cambios en el cronograma de las clases a programar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estar preparados para eventualidades agenas a la empresa, asi poder reacomodar o eliminar una clase </t>
-  </si>
-  <si>
     <t>HU_004</t>
   </si>
   <si>
-    <t>RE_007</t>
-  </si>
-  <si>
-    <t>Secretaria</t>
-  </si>
-  <si>
-    <t>Dejar que los clientes puedan programar sus propias clases</t>
-  </si>
-  <si>
-    <t>Disminuir la carga de la secretaria haciendo el proceso de la insciripcion de clases</t>
-  </si>
-  <si>
     <t>HU_005</t>
   </si>
   <si>
-    <t>RE_008</t>
-  </si>
-  <si>
     <t>Profesor</t>
   </si>
   <si>
-    <t>Tener un listado de asistencia y faltas par llevar un control de las clases que se dan y a la cantidad que se le dan</t>
-  </si>
-  <si>
-    <t>Poder generar un informe de la cantidad de clases que se dan asi como a cuantos clientes se le dan clases</t>
-  </si>
-  <si>
     <t>HU_006</t>
   </si>
   <si>
-    <t>RE_009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tener una posibilidad de mostrar a los clientes su progreso segun el profesor calificador </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poder mantener un historial de "calificaciones" en donde el cliente pueda ver dicho avance </t>
-  </si>
-  <si>
     <t>HU_007</t>
   </si>
   <si>
-    <t>RE_010</t>
-  </si>
-  <si>
-    <t>Poder definir que usuario es profesor cliente y secretaria</t>
-  </si>
-  <si>
-    <t>Dar orden al sistema y en los lugares deonde cada usuario podra acceder</t>
-  </si>
-  <si>
     <t>HU_008</t>
   </si>
   <si>
-    <t>RE_011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poder gestionar el calendario por medio de la aplicacion con sus recordatorios </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generar una facilidad para poder recordar las clases programadas </t>
-  </si>
-  <si>
     <t>HU_009</t>
   </si>
   <si>
-    <t>RE_012</t>
-  </si>
-  <si>
-    <t>Tener una notificacion facil y rapida donde el cliente podra decir si asistira o no a clase</t>
-  </si>
-  <si>
-    <t>tTener mayor asistencia y/o depejar lugares a clases que ya no tenian espacio</t>
-  </si>
-  <si>
     <t>HU_010</t>
   </si>
   <si>
-    <t>RE_013</t>
-  </si>
-  <si>
-    <t>Tener una forma de mostrar los eventos en los cuales esta involucrada la escuela</t>
-  </si>
-  <si>
-    <t>Dar mas visibilidad a este punto</t>
-  </si>
-  <si>
     <t>HU_011</t>
   </si>
   <si>
-    <t>RE_014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tener una facilidad a la hora de registrar el desempeño del cliente </t>
-  </si>
-  <si>
-    <t>poder generar un informe individual del cliente echo por el profesor que le imparte la clase</t>
-  </si>
-  <si>
     <t>HU_012</t>
   </si>
   <si>
-    <t xml:space="preserve">RENF_001 al RENF_003 y RENF_005 al RENF_007 </t>
-  </si>
-  <si>
-    <t>La pagina debe ser accesible por todos, asi mismo debe ser rapida y facil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podra dar mas visibilidad a la escuela, al llegar a mas personas </t>
-  </si>
-  <si>
     <t>HU_013</t>
   </si>
   <si>
-    <t>RENF_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">la pagina debe asegurar que los datos ingresados no podran ser mostrados por alguien que no sea el mismo usuario </t>
-  </si>
-  <si>
-    <t>Dar mas seguridad a la pagina para lograr tener la confianza de los usuarios</t>
-  </si>
-  <si>
-    <t>HU_014</t>
-  </si>
-  <si>
-    <t>RENF_008</t>
-  </si>
-  <si>
-    <t>HU_015</t>
-  </si>
-  <si>
-    <t>RENF_009 y RENF_010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tener una forma rapida decalificar a los clientes que estan durante la clase </t>
-  </si>
-  <si>
-    <t>Tener un formato ya predestinado parauna eficacia rapida a la hora de evaluar</t>
-  </si>
-  <si>
-    <t>HU_016</t>
-  </si>
-  <si>
-    <t>RENF_011 al RENF_013</t>
-  </si>
-  <si>
-    <t>Tener la posibilidad de tener un informe de uso sobre sus clientes y profesores en la escuela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contener la informacion con la posibilidad de tener informes de manera mas eficiente </t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sofware debe ser facil de entender y actualizar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dar mas facilidades y posibilidades de una actualizacion </t>
+    <t>riesgo en desarrollo</t>
+  </si>
+  <si>
+    <t>prioridad</t>
+  </si>
+  <si>
+    <t>Validación</t>
+  </si>
+  <si>
+    <t>Usuario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quiero que el programa me permita crear usuarios queincluya sus datos basicos </t>
+  </si>
+  <si>
+    <t>ALTA</t>
+  </si>
+  <si>
+    <t>BAJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El cliente debe podar crear un usuario, y darle atributos de informacion personal </t>
+  </si>
+  <si>
+    <t>Dueño / Cliente</t>
+  </si>
+  <si>
+    <t>Quiero poder editar los datos de los usuarios, como nombre y datos de contacto.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir la modificación de datos de los usuarios según los permisos establecidos.</t>
+  </si>
+  <si>
+    <t>MEDIA</t>
+  </si>
+  <si>
+    <t>Quiero poder eliminar usuarios que ya no formen parte de la empresa (estudiantes o profesores) para evitar registros innecesarios.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir la eliminación de usuarios de manera segura sin afectar datos históricos.</t>
+  </si>
+  <si>
+    <t>Quiero poder visualizar a todos los estudiantes y/o profesores inscritos en ese momento.</t>
+  </si>
+  <si>
+    <t>El sistema debe mostrar una lista de usuarios filtrada por rol.</t>
+  </si>
+  <si>
+    <t>Quiero poder crear clases, manipular el calendario y asignar un profesor, tipo de baile, nivel y horario.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir la creación de clases con toda la información requerida.</t>
+  </si>
+  <si>
+    <t>Quiero poder editar los detalles de una clase.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir modificar datos como horario, profesor y tipo de baile.</t>
+  </si>
+  <si>
+    <t>Quiero poder eliminar una clase cuando sea necesario.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir la eliminación de clases sin afectar el historial de asistencia.</t>
+  </si>
+  <si>
+    <t>Quiero que los clientes puedan inscribirse en una clase y ver la información de nivel, profesor y horario.</t>
+  </si>
+  <si>
+    <t>Los clientes deben poder seleccionar una clase y confirmar su inscripción.</t>
+  </si>
+  <si>
+    <t>Quiero poder registrar la asistencia de los estudiantes inscritos en mi clase.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir marcar si un estudiante asistió o no a la clase.</t>
+  </si>
+  <si>
+    <t>Quiero visualizar informes sobre alumnos, clases y asistencia para evaluar la tasa de asistencia.</t>
+  </si>
+  <si>
+    <t>El sistema debe generar reportes con métricas sobre asistencia y participación.</t>
+  </si>
+  <si>
+    <t>Quiero poder crear eventos de la escuela.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir la creación de eventos con fecha, descripción e imágenes.</t>
+  </si>
+  <si>
+    <t>Quiero poder editar eventos de la escuela.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir la modificación de eventos creados.</t>
+  </si>
+  <si>
+    <t>Quiero poder eliminar eventos de la escuela.</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir eliminar eventos sin afectar otros módulos.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -265,12 +202,6 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -286,7 +217,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -309,6 +240,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -321,7 +263,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -542,321 +484,313 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B1:F983"/>
+  <dimension ref="A1:F980"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.28515625" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" customWidth="1"/>
+    <col min="4" max="4" width="33.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="2:6" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="2:6" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
+    <row r="6" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="57" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="13" spans="2:6" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    <row r="14" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="14" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="2" t="s">
+    <row r="16" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>51</v>
+      <c r="E16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1805,15 +1739,13 @@
     <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D19" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Dueño,Profesor,Secretaria"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>